--- a/jpcore-r4/feature/fix-tx-error/observations-summary.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="63">
   <si>
     <t>Profile</t>
   </si>
@@ -80,13 +80,13 @@
     <t>null#procedure</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS (required)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS (example)</t>
   </si>
   <si>
     <t>null#11524-6</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS (preferred)</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
@@ -162,9 +162,6 @@
   </si>
   <si>
     <t>null#18782-3</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
   </si>
   <si>
     <t>dateTime</t>
@@ -602,13 +599,13 @@
         <v>49</v>
       </c>
       <c r="F8" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="G8" t="s" s="2">
+      <c r="H8" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>52</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -622,28 +619,28 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="B9" t="s" s="2">
+      <c r="C9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="C9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>55</v>
-      </c>
       <c r="F9" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="G9" t="s" s="2">
+      <c r="H9" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>52</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -657,22 +654,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="C10" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="C10" t="s" s="2">
+      <c r="D10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s" s="2">
         <v>58</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s" s="2">
-        <v>59</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>16</v>
@@ -692,22 +689,22 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="C11" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="C11" t="s" s="2">
+      <c r="D11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s" s="2">
         <v>62</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F11" t="s" s="2">
-        <v>63</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>16</v>
